--- a/data/genericballot.xlsx
+++ b/data/genericballot.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="28">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -104,9 +104,6 @@
   </si>
   <si>
     <t xml:space="preserve">Marist Poll/NPR/PBS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarity Labs</t>
   </si>
 </sst>
 </file>
@@ -182,21 +179,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -346,11 +335,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.2"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.83"/>
   </cols>
   <sheetData>
@@ -367,7 +355,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -378,19 +366,19 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="1" t="n">
         <v>1500</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -401,19 +389,19 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="1" t="n">
         <v>1500</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -424,19 +412,19 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="1" t="n">
         <v>1500</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -447,7 +435,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="2" t="n">
         <v>45718</v>
       </c>
       <c r="B5" s="1" t="n">
@@ -459,7 +447,7 @@
       <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="1" t="n">
         <v>1000</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -470,7 +458,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="2" t="n">
         <v>45718</v>
       </c>
       <c r="B6" s="1" t="n">
@@ -482,7 +470,7 @@
       <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="1" t="n">
         <v>1000</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -493,7 +481,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="2" t="n">
         <v>45718</v>
       </c>
       <c r="B7" s="1" t="n">
@@ -505,7 +493,7 @@
       <c r="D7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="1" t="n">
         <v>1000</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -516,19 +504,19 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="2" t="n">
         <v>45721</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="1" t="n">
         <v>1500</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -539,19 +527,19 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="2" t="n">
         <v>45721</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="1" t="n">
         <v>1500</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -562,19 +550,19 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="2" t="n">
         <v>45721</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="1" t="n">
         <v>1500</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -585,19 +573,19 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="2" t="n">
         <v>45750</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="1" t="n">
         <v>1500</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -608,19 +596,19 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="2" t="n">
         <v>45750</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="1" t="n">
         <v>1500</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -631,19 +619,19 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="2" t="n">
         <v>45750</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="1" t="n">
         <v>1500</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -654,7 +642,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="2" t="n">
         <v>45760</v>
       </c>
       <c r="B14" s="1" t="n">
@@ -666,7 +654,7 @@
       <c r="D14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="1" t="n">
         <v>1000</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -677,7 +665,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="2" t="n">
         <v>45760</v>
       </c>
       <c r="B15" s="1" t="n">
@@ -689,7 +677,7 @@
       <c r="D15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="1" t="n">
         <v>1000</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -700,7 +688,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="2" t="n">
         <v>45760</v>
       </c>
       <c r="B16" s="1" t="n">
@@ -712,7 +700,7 @@
       <c r="D16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="1" t="n">
         <v>1000</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -723,19 +711,19 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="1" t="n">
         <v>1500</v>
       </c>
       <c r="F17" s="1" t="s">
@@ -746,19 +734,19 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="1" t="n">
         <v>1500</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -769,19 +757,19 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="1" t="n">
         <v>1500</v>
       </c>
       <c r="F19" s="1" t="s">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="2" t="n">
         <v>45804</v>
       </c>
       <c r="B20" s="1" t="n">
@@ -804,7 +792,7 @@
       <c r="D20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="1" t="n">
         <v>3469</v>
       </c>
       <c r="F20" s="1" t="s">
@@ -815,7 +803,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="2" t="n">
         <v>45804</v>
       </c>
       <c r="B21" s="1" t="n">
@@ -827,7 +815,7 @@
       <c r="D21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="1" t="n">
         <v>3469</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -838,7 +826,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="2" t="n">
         <v>45804</v>
       </c>
       <c r="B22" s="1" t="n">
@@ -850,7 +838,7 @@
       <c r="D22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="1" t="n">
         <v>3469</v>
       </c>
       <c r="F22" s="1" t="s">
@@ -861,19 +849,19 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="2" t="n">
         <v>45811</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="1" t="n">
         <v>1500</v>
       </c>
       <c r="F23" s="1" t="s">
@@ -884,19 +872,19 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="2" t="n">
         <v>45811</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="1" t="n">
         <v>1500</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -907,13 +895,13 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="2" t="n">
         <v>45811</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -922,15 +910,15 @@
       <c r="E25" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="F25" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G25" s="6" t="s">
+      <c r="F25" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="B26" s="1" t="n">
@@ -942,7 +930,7 @@
       <c r="D26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="1" t="n">
         <v>800</v>
       </c>
       <c r="F26" s="1" t="s">
@@ -953,7 +941,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="B27" s="1" t="n">
@@ -965,7 +953,7 @@
       <c r="D27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="1" t="n">
         <v>800</v>
       </c>
       <c r="F27" s="1" t="s">
@@ -976,7 +964,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="B28" s="1" t="n">
@@ -988,7 +976,7 @@
       <c r="D28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="1" t="n">
         <v>800</v>
       </c>
       <c r="F28" s="1" t="s">
@@ -999,7 +987,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="B29" s="1" t="n">
@@ -1011,7 +999,7 @@
       <c r="D29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="1" t="n">
         <v>1500</v>
       </c>
       <c r="F29" s="1" t="s">
@@ -1022,7 +1010,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="B30" s="1" t="n">
@@ -1034,7 +1022,7 @@
       <c r="D30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="1" t="n">
         <v>1500</v>
       </c>
       <c r="F30" s="1" t="s">
@@ -1045,7 +1033,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="B31" s="1" t="n">
@@ -1057,7 +1045,7 @@
       <c r="D31" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="1" t="n">
         <v>1500</v>
       </c>
       <c r="F31" s="1" t="s">
@@ -1068,7 +1056,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B32" s="1" t="n">
@@ -1080,7 +1068,7 @@
       <c r="D32" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="1" t="n">
         <v>1935</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -1091,7 +1079,7 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B33" s="1" t="n">
@@ -1103,7 +1091,7 @@
       <c r="D33" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="1" t="n">
         <v>1935</v>
       </c>
       <c r="F33" s="1" t="s">
@@ -1114,7 +1102,7 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B34" s="1" t="n">
@@ -1126,7 +1114,7 @@
       <c r="D34" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="1" t="n">
         <v>1935</v>
       </c>
       <c r="F34" s="1" t="s">
@@ -1137,7 +1125,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="B35" s="1" t="n">
@@ -1149,7 +1137,7 @@
       <c r="D35" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="1" t="n">
         <v>1400</v>
       </c>
       <c r="F35" s="1" t="s">
@@ -1160,7 +1148,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="B36" s="1" t="n">
@@ -1172,7 +1160,7 @@
       <c r="D36" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="1" t="n">
         <v>1400</v>
       </c>
       <c r="F36" s="1" t="s">
@@ -1183,7 +1171,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="B37" s="1" t="n">
@@ -1195,7 +1183,7 @@
       <c r="D37" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="1" t="n">
         <v>1400</v>
       </c>
       <c r="F37" s="1" t="s">
@@ -1206,7 +1194,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B38" s="1" t="n">
@@ -1218,7 +1206,7 @@
       <c r="D38" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="1" t="n">
         <v>1000</v>
       </c>
       <c r="F38" s="1" t="s">
@@ -1229,7 +1217,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B39" s="1" t="n">
@@ -1241,7 +1229,7 @@
       <c r="D39" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="1" t="n">
         <v>1000</v>
       </c>
       <c r="F39" s="1" t="s">
@@ -1252,7 +1240,7 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B40" s="1" t="n">
@@ -1264,7 +1252,7 @@
       <c r="D40" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="1" t="n">
         <v>1000</v>
       </c>
       <c r="F40" s="1" t="s">
@@ -1275,7 +1263,7 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="2" t="n">
         <v>45878</v>
       </c>
       <c r="B41" s="1" t="n">
@@ -1287,10 +1275,10 @@
       <c r="D41" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="1" t="n">
         <v>1500</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G41" s="1" t="s">
@@ -1298,7 +1286,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="2" t="n">
         <v>45878</v>
       </c>
       <c r="B42" s="1" t="n">
@@ -1310,10 +1298,10 @@
       <c r="D42" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="1" t="n">
         <v>1500</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G42" s="1" t="s">
@@ -1321,7 +1309,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="n">
+      <c r="A43" s="2" t="n">
         <v>45878</v>
       </c>
       <c r="B43" s="1" t="n">
@@ -1333,10 +1321,10 @@
       <c r="D43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="1" t="n">
         <v>1500</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F43" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G43" s="1" t="s">
@@ -1344,7 +1332,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="n">
+      <c r="A44" s="2" t="n">
         <v>45886</v>
       </c>
       <c r="B44" s="1" t="n">
@@ -1356,10 +1344,10 @@
       <c r="D44" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="1" t="n">
         <v>1057</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="F44" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G44" s="1" t="s">
@@ -1367,7 +1355,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="n">
+      <c r="A45" s="2" t="n">
         <v>45886</v>
       </c>
       <c r="B45" s="1" t="n">
@@ -1379,10 +1367,10 @@
       <c r="D45" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="1" t="n">
         <v>1057</v>
       </c>
-      <c r="F45" s="6" t="s">
+      <c r="F45" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G45" s="1" t="s">
@@ -1390,7 +1378,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="2" t="n">
         <v>45886</v>
       </c>
       <c r="B46" s="1" t="n">
@@ -1402,10 +1390,10 @@
       <c r="D46" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="1" t="n">
         <v>1057</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F46" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G46" s="1" t="s">
@@ -1413,22 +1401,22 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="n">
+      <c r="A47" s="2" t="n">
         <v>45895</v>
       </c>
       <c r="B47" s="1" t="n">
         <v>43.3</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G47" s="1" t="s">
@@ -1436,22 +1424,22 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="n">
+      <c r="A48" s="2" t="n">
         <v>45895</v>
       </c>
       <c r="B48" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="F48" s="6" t="s">
+      <c r="F48" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G48" s="1" t="s">
@@ -1459,22 +1447,22 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="2" t="n">
         <v>45895</v>
       </c>
       <c r="B49" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="1" t="n">
         <v>1066</v>
       </c>
-      <c r="F49" s="6" t="s">
+      <c r="F49" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G49" s="1" t="s">
@@ -1482,22 +1470,22 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="B50" s="1" t="n">
         <v>51.8</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="E50" s="1" t="n">
         <v>1066</v>
       </c>
-      <c r="F50" s="6" t="s">
+      <c r="F50" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G50" s="1" t="s">
@@ -1505,22 +1493,22 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="B51" s="1" t="n">
         <v>43.5</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="E51" s="1" t="n">
         <v>1066</v>
       </c>
-      <c r="F51" s="6" t="s">
+      <c r="F51" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G51" s="1" t="s">
@@ -1528,22 +1516,22 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="B52" s="1" t="n">
         <v>3.9</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="E52" s="1" t="n">
         <v>1066</v>
       </c>
-      <c r="F52" s="6" t="s">
+      <c r="F52" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G52" s="1" t="s">
@@ -1551,22 +1539,22 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="n">
+      <c r="A53" s="2" t="n">
         <v>45922</v>
       </c>
       <c r="B53" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="E53" s="1" t="n">
         <v>1071</v>
       </c>
-      <c r="F53" s="6" t="s">
+      <c r="F53" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G53" s="1" t="s">
@@ -1574,22 +1562,22 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="n">
+      <c r="A54" s="2" t="n">
         <v>45922</v>
       </c>
       <c r="B54" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="E54" s="1" t="n">
         <v>1071</v>
       </c>
-      <c r="F54" s="6" t="s">
+      <c r="F54" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G54" s="1" t="s">
@@ -1597,22 +1585,22 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="n">
+      <c r="A55" s="2" t="n">
         <v>45922</v>
       </c>
       <c r="B55" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="E55" s="1" t="n">
         <v>1071</v>
       </c>
-      <c r="F55" s="6" t="s">
+      <c r="F55" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G55" s="1" t="s">
@@ -1620,22 +1608,22 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="n">
+      <c r="A56" s="2" t="n">
         <v>45927</v>
       </c>
       <c r="B56" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="E56" s="1" t="n">
         <v>1313</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="F56" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G56" s="1" t="s">
@@ -1643,22 +1631,22 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="n">
+      <c r="A57" s="2" t="n">
         <v>45927</v>
       </c>
       <c r="B57" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="E57" s="1" t="n">
         <v>1313</v>
       </c>
-      <c r="F57" s="6" t="s">
+      <c r="F57" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G57" s="1" t="s">
@@ -1666,22 +1654,22 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="n">
+      <c r="A58" s="2" t="n">
         <v>45927</v>
       </c>
       <c r="B58" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="E58" s="1" t="n">
         <v>1313</v>
       </c>
-      <c r="F58" s="6" t="s">
+      <c r="F58" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G58" s="1" t="s">
@@ -1689,22 +1677,22 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="n">
+      <c r="A59" s="2" t="n">
         <v>45938</v>
       </c>
       <c r="B59" s="1" t="n">
         <v>47.5</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="E59" s="1" t="n">
         <v>1500</v>
       </c>
-      <c r="F59" s="6" t="s">
+      <c r="F59" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G59" s="1" t="s">
@@ -1712,22 +1700,22 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="n">
+      <c r="A60" s="2" t="n">
         <v>45938</v>
       </c>
       <c r="B60" s="1" t="n">
         <v>45.3</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="E60" s="1" t="n">
         <v>1500</v>
       </c>
-      <c r="F60" s="6" t="s">
+      <c r="F60" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G60" s="1" t="s">
@@ -1735,22 +1723,22 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="n">
+      <c r="A61" s="2" t="n">
         <v>45938</v>
       </c>
       <c r="B61" s="1" t="n">
         <v>7.3</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E61" s="3" t="n">
+      <c r="E61" s="1" t="n">
         <v>1500</v>
       </c>
-      <c r="F61" s="6" t="s">
+      <c r="F61" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G61" s="1" t="s">
@@ -1758,22 +1746,22 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="n">
+      <c r="A62" s="2" t="n">
         <v>45944</v>
       </c>
       <c r="B62" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E62" s="3" t="n">
+      <c r="E62" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="F62" s="6" t="s">
+      <c r="F62" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G62" s="1" t="s">
@@ -1781,22 +1769,22 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="n">
+      <c r="A63" s="2" t="n">
         <v>45944</v>
       </c>
       <c r="B63" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E63" s="3" t="n">
+      <c r="E63" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="F63" s="6" t="s">
+      <c r="F63" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G63" s="1" t="s">
@@ -1804,22 +1792,22 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="n">
+      <c r="A64" s="2" t="n">
         <v>45944</v>
       </c>
       <c r="B64" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E64" s="3" t="n">
+      <c r="E64" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="F64" s="6" t="s">
+      <c r="F64" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G64" s="1" t="s">
@@ -1827,22 +1815,22 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="n">
+      <c r="A65" s="2" t="n">
         <v>45950</v>
       </c>
       <c r="B65" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E65" s="3" t="n">
+      <c r="E65" s="1" t="n">
         <v>1327</v>
       </c>
-      <c r="F65" s="6" t="s">
+      <c r="F65" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G65" s="1" t="s">
@@ -1850,22 +1838,22 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="n">
+      <c r="A66" s="2" t="n">
         <v>45950</v>
       </c>
       <c r="B66" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E66" s="3" t="n">
+      <c r="E66" s="1" t="n">
         <v>1327</v>
       </c>
-      <c r="F66" s="6" t="s">
+      <c r="F66" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G66" s="1" t="s">
@@ -1873,22 +1861,22 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="n">
+      <c r="A67" s="2" t="n">
         <v>45950</v>
       </c>
       <c r="B67" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E67" s="3" t="n">
+      <c r="E67" s="1" t="n">
         <v>1327</v>
       </c>
-      <c r="F67" s="6" t="s">
+      <c r="F67" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G67" s="1" t="s">
@@ -1896,22 +1884,22 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="n">
+      <c r="A68" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="B68" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E68" s="3" t="n">
+      <c r="E68" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="F68" s="6" t="s">
+      <c r="F68" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G68" s="1" t="s">
@@ -1919,22 +1907,22 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="n">
+      <c r="A69" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="B69" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="C69" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E69" s="3" t="n">
+      <c r="E69" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="F69" s="6" t="s">
+      <c r="F69" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G69" s="1" t="s">
@@ -1942,22 +1930,22 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="n">
+      <c r="A70" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="B70" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C70" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E70" s="3" t="n">
+      <c r="E70" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="F70" s="6" t="s">
+      <c r="F70" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G70" s="1" t="s">
@@ -1965,22 +1953,22 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="n">
+      <c r="A71" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="B71" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E71" s="3" t="n">
+      <c r="E71" s="1" t="n">
         <v>1245</v>
       </c>
-      <c r="F71" s="6" t="s">
+      <c r="F71" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G71" s="1" t="s">
@@ -1988,22 +1976,22 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4" t="n">
+      <c r="A72" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="B72" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C72" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E72" s="3" t="n">
+      <c r="E72" s="1" t="n">
         <v>1245</v>
       </c>
-      <c r="F72" s="6" t="s">
+      <c r="F72" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G72" s="1" t="s">
@@ -2011,22 +1999,22 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="4" t="n">
+      <c r="A73" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="B73" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C73" s="6" t="s">
+      <c r="C73" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E73" s="3" t="n">
+      <c r="E73" s="1" t="n">
         <v>1245</v>
       </c>
-      <c r="F73" s="6" t="s">
+      <c r="F73" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G73" s="1" t="s">
@@ -2034,22 +2022,22 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="n">
+      <c r="A74" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="B74" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="C74" s="6" t="s">
+      <c r="C74" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E74" s="3" t="n">
+      <c r="E74" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="F74" s="6" t="s">
+      <c r="F74" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G74" s="1" t="s">
@@ -2057,22 +2045,22 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="B75" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="C75" s="6" t="s">
+      <c r="C75" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E75" s="3" t="n">
+      <c r="E75" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="F75" s="6" t="s">
+      <c r="F75" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G75" s="1" t="s">
@@ -2080,22 +2068,22 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="n">
+      <c r="A76" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="B76" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E76" s="3" t="n">
+      <c r="E76" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="F76" s="6" t="s">
+      <c r="F76" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G76" s="1" t="s">
@@ -2103,22 +2091,22 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="n">
+      <c r="A77" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="B77" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="C77" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E77" s="3" t="n">
+      <c r="E77" s="1" t="n">
         <v>903</v>
       </c>
-      <c r="F77" s="6" t="s">
+      <c r="F77" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G77" s="1" t="s">
@@ -2126,22 +2114,22 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="n">
+      <c r="A78" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="B78" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="C78" s="6" t="s">
+      <c r="C78" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E78" s="3" t="n">
+      <c r="E78" s="1" t="n">
         <v>903</v>
       </c>
-      <c r="F78" s="6" t="s">
+      <c r="F78" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G78" s="1" t="s">
@@ -2149,22 +2137,22 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="n">
+      <c r="A79" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="B79" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="C79" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E79" s="3" t="n">
+      <c r="E79" s="1" t="n">
         <v>903</v>
       </c>
-      <c r="F79" s="6" t="s">
+      <c r="F79" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G79" s="1" t="s">
@@ -2172,22 +2160,22 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="n">
+      <c r="A80" s="2" t="n">
         <v>45974</v>
       </c>
       <c r="B80" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="C80" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D80" s="7" t="s">
+      <c r="C80" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E80" s="3" t="n">
+      <c r="E80" s="1" t="n">
         <v>1219</v>
       </c>
-      <c r="F80" s="6" t="s">
+      <c r="F80" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G80" s="1" t="s">
@@ -2195,22 +2183,22 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="4" t="n">
+      <c r="A81" s="2" t="n">
         <v>45974</v>
       </c>
       <c r="B81" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="C81" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D81" s="7" t="s">
+      <c r="C81" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E81" s="3" t="n">
+      <c r="E81" s="1" t="n">
         <v>1219</v>
       </c>
-      <c r="F81" s="6" t="s">
+      <c r="F81" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G81" s="1" t="s">
@@ -2218,22 +2206,22 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="4" t="n">
+      <c r="A82" s="2" t="n">
         <v>45974</v>
       </c>
       <c r="B82" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C82" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D82" s="7" t="s">
+      <c r="C82" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D82" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E82" s="3" t="n">
+      <c r="E82" s="1" t="n">
         <v>1219</v>
       </c>
-      <c r="F82" s="6" t="s">
+      <c r="F82" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G82" s="1" t="s">
@@ -2241,22 +2229,22 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="4" t="n">
+      <c r="A83" s="2" t="n">
         <v>45978</v>
       </c>
       <c r="B83" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="C83" s="6" t="s">
+      <c r="C83" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E83" s="3" t="n">
+      <c r="E83" s="1" t="n">
         <v>1051</v>
       </c>
-      <c r="F83" s="6" t="s">
+      <c r="F83" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G83" s="1" t="s">
@@ -2264,22 +2252,22 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4" t="n">
+      <c r="A84" s="2" t="n">
         <v>45978</v>
       </c>
       <c r="B84" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="C84" s="6" t="s">
+      <c r="C84" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E84" s="3" t="n">
+      <c r="E84" s="1" t="n">
         <v>1051</v>
       </c>
-      <c r="F84" s="6" t="s">
+      <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G84" s="1" t="s">
@@ -2287,22 +2275,22 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4" t="n">
+      <c r="A85" s="2" t="n">
         <v>45978</v>
       </c>
       <c r="B85" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C85" s="6" t="s">
+      <c r="C85" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E85" s="3" t="n">
+      <c r="E85" s="1" t="n">
         <v>1051</v>
       </c>
-      <c r="F85" s="6" t="s">
+      <c r="F85" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G85" s="1" t="s">
@@ -2310,330 +2298,141 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4" t="n">
-        <v>46002</v>
+      <c r="A86" s="2" t="n">
+        <v>46039</v>
       </c>
       <c r="B86" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="C86" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E86" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E86" s="1" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2" t="n">
+        <v>46039</v>
+      </c>
+      <c r="B87" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E87" s="1" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2" t="n">
+        <v>46039</v>
+      </c>
+      <c r="B88" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E88" s="1" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="6" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B89" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" s="0" t="n">
         <v>1000</v>
       </c>
-      <c r="F86" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="n">
-        <v>46002</v>
-      </c>
-      <c r="B87" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E87" s="2" t="n">
+      <c r="F89" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="6" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B90" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" s="0" t="n">
         <v>1000</v>
       </c>
-      <c r="F87" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="n">
-        <v>46002</v>
-      </c>
-      <c r="B88" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E88" s="2" t="n">
+      <c r="F90" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="6" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B91" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" s="0" t="n">
         <v>1000</v>
       </c>
-      <c r="F88" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4" t="n">
-        <v>46006</v>
-      </c>
-      <c r="B89" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E89" s="2" t="n">
-        <v>1011</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="4" t="n">
-        <v>46006</v>
-      </c>
-      <c r="B90" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>1011</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="4" t="n">
-        <v>46006</v>
-      </c>
-      <c r="B91" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E91" s="2" t="n">
-        <v>1011</v>
-      </c>
-      <c r="F91" s="6" t="s">
+      <c r="F91" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="4" t="n">
-        <v>46006</v>
-      </c>
-      <c r="B92" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>1035</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="4" t="n">
-        <v>46006</v>
-      </c>
-      <c r="B93" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>1035</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="4" t="n">
-        <v>46006</v>
-      </c>
-      <c r="B94" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E94" s="3" t="n">
-        <v>1035</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4" t="n">
-        <v>46006</v>
-      </c>
-      <c r="B95" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E95" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="n">
-        <v>46006</v>
-      </c>
-      <c r="B96" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="4" t="n">
-        <v>46006</v>
-      </c>
-      <c r="B97" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F97" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="8" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B98" s="0" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>2315</v>
-      </c>
-      <c r="F98" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="8" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B99" s="0" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>2315</v>
-      </c>
-      <c r="F99" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="8" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B100" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>2315</v>
-      </c>
-      <c r="F100" s="9" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/data/genericballot.xlsx
+++ b/data/genericballot.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="28">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -335,7 +335,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.2"/>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="n">
-        <v>46039</v>
+        <v>46030</v>
       </c>
       <c r="B86" s="1" t="n">
-        <v>48</v>
+        <v>48.2</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>1625</v>
+        <v>1500</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>10</v>
@@ -2322,22 +2322,22 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="n">
-        <v>46039</v>
+        <v>46030</v>
       </c>
       <c r="B87" s="1" t="n">
-        <v>43</v>
+        <v>44.6</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>1625</v>
+        <v>1500</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>10</v>
@@ -2345,94 +2345,232 @@
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B88" s="1" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E88" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="n">
         <v>46039</v>
       </c>
-      <c r="B88" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D88" s="1" t="s">
+      <c r="B89" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E88" s="1" t="n">
+      <c r="E89" s="1" t="n">
         <v>1625</v>
       </c>
-      <c r="F88" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="6" t="n">
+      <c r="F89" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="n">
+        <v>46039</v>
+      </c>
+      <c r="B90" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E90" s="1" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2" t="n">
+        <v>46039</v>
+      </c>
+      <c r="B91" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E91" s="1" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2" t="n">
         <v>46041</v>
       </c>
-      <c r="B89" s="0" t="n">
+      <c r="B92" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="C89" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D89" s="1" t="s">
+      <c r="C92" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E89" s="0" t="n">
+      <c r="E92" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="F89" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G89" s="1" t="s">
+      <c r="F92" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G92" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="6" t="n">
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="n">
         <v>46041</v>
       </c>
-      <c r="B90" s="0" t="n">
+      <c r="B93" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="C90" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D90" s="1" t="s">
+      <c r="C93" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E90" s="0" t="n">
+      <c r="E93" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="F90" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G90" s="1" t="s">
+      <c r="F93" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G93" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="6" t="n">
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2" t="n">
         <v>46041</v>
       </c>
-      <c r="B91" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D91" s="1" t="s">
+      <c r="B94" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E91" s="0" t="n">
+      <c r="E94" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="F91" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G91" s="1" t="s">
+      <c r="F94" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G94" s="1" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="6" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B95" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E95" s="0" t="n">
+        <v>1029</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="6" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B96" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E96" s="0" t="n">
+        <v>1029</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="6" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B97" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E97" s="0" t="n">
+        <v>1029</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/genericballot.xlsx
+++ b/data/genericballot.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="29">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t xml:space="preserve">Marist Poll/NPR/PBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focaldata</t>
   </si>
 </sst>
 </file>
@@ -335,7 +338,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.2"/>
@@ -2505,10 +2508,10 @@
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="6" t="n">
+      <c r="A95" s="2" t="n">
         <v>46048</v>
       </c>
-      <c r="B95" s="0" t="n">
+      <c r="B95" s="1" t="n">
         <v>49</v>
       </c>
       <c r="C95" s="4" t="s">
@@ -2517,10 +2520,10 @@
       <c r="D95" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E95" s="0" t="n">
+      <c r="E95" s="1" t="n">
         <v>1029</v>
       </c>
-      <c r="F95" s="7" t="s">
+      <c r="F95" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G95" s="1" t="s">
@@ -2528,10 +2531,10 @@
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="6" t="n">
+      <c r="A96" s="2" t="n">
         <v>46048</v>
       </c>
-      <c r="B96" s="0" t="n">
+      <c r="B96" s="1" t="n">
         <v>44</v>
       </c>
       <c r="C96" s="4" t="s">
@@ -2540,10 +2543,10 @@
       <c r="D96" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E96" s="0" t="n">
+      <c r="E96" s="1" t="n">
         <v>1029</v>
       </c>
-      <c r="F96" s="7" t="s">
+      <c r="F96" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G96" s="1" t="s">
@@ -2551,10 +2554,10 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="6" t="n">
+      <c r="A97" s="2" t="n">
         <v>46048</v>
       </c>
-      <c r="B97" s="0" t="n">
+      <c r="B97" s="1" t="n">
         <v>7</v>
       </c>
       <c r="C97" s="4" t="s">
@@ -2563,14 +2566,212 @@
       <c r="D97" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E97" s="0" t="n">
+      <c r="E97" s="1" t="n">
         <v>1029</v>
       </c>
-      <c r="F97" s="7" t="s">
+      <c r="F97" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B98" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E98" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B99" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E99" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E100" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B101" s="1" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B102" s="1" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E102" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B103" s="1" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E103" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="6" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B104" s="0" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E104" s="0" t="n">
+        <v>1148</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="6" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B105" s="0" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E105" s="0" t="n">
+        <v>1148</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="6" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B106" s="0" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E106" s="0" t="n">
+        <v>1148</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/genericballot.xlsx
+++ b/data/genericballot.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="29">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -207,11 +207,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -338,7 +338,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.2"/>
@@ -2715,10 +2715,10 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="6" t="n">
+      <c r="A104" s="2" t="n">
         <v>46063</v>
       </c>
-      <c r="B104" s="0" t="n">
+      <c r="B104" s="1" t="n">
         <v>51.1</v>
       </c>
       <c r="C104" s="4" t="s">
@@ -2727,18 +2727,18 @@
       <c r="D104" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E104" s="0" t="n">
+      <c r="E104" s="1" t="n">
         <v>1148</v>
       </c>
-      <c r="F104" s="7" t="s">
+      <c r="F104" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="6" t="n">
+      <c r="A105" s="2" t="n">
         <v>46063</v>
       </c>
-      <c r="B105" s="0" t="n">
+      <c r="B105" s="1" t="n">
         <v>43.6</v>
       </c>
       <c r="C105" s="4" t="s">
@@ -2747,18 +2747,18 @@
       <c r="D105" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E105" s="0" t="n">
+      <c r="E105" s="1" t="n">
         <v>1148</v>
       </c>
-      <c r="F105" s="7" t="s">
+      <c r="F105" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="6" t="n">
+      <c r="A106" s="2" t="n">
         <v>46063</v>
       </c>
-      <c r="B106" s="0" t="n">
+      <c r="B106" s="1" t="n">
         <v>5.3</v>
       </c>
       <c r="C106" s="4" t="s">
@@ -2767,11 +2767,149 @@
       <c r="D106" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E106" s="0" t="n">
+      <c r="E106" s="1" t="n">
         <v>1148</v>
       </c>
-      <c r="F106" s="7" t="s">
-        <v>9</v>
+      <c r="F106" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B107" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B108" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E108" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B109" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E109" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="7" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B110" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E110" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="7" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B111" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E111" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="7" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B112" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E112" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
